--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run7/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run7/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9052,0.0385,0.0092,0.0283</t>
-  </si>
-  <si>
-    <t>0.0131,0.0015,0.0009,0.9932</t>
-  </si>
-  <si>
-    <t>0.9726,0.0035,0.0008,0.0139</t>
-  </si>
-  <si>
-    <t>0.0704,0.0076,0.0011,0.9560</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9976,0.0006,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9958,0.0027,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9976,0.0031,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0009,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0006,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.8070,0.0027,0.3316,0.0020</t>
-  </si>
-  <si>
-    <t>0.0326,0.0140,0.9632,0.0044</t>
-  </si>
-  <si>
-    <t>0.0806,0.0062,0.9435,0.0013</t>
-  </si>
-  <si>
-    <t>0.0120,0.0162,0.9612,0.0167</t>
-  </si>
-  <si>
-    <t>0.8427,0.0079,0.1482,0.0125</t>
-  </si>
-  <si>
-    <t>0.0001,0.9994,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.9952,0.0058,0.0016</t>
-  </si>
-  <si>
-    <t>0.0545,0.9603,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.0031,0.9913,0.0040,0.0038</t>
-  </si>
-  <si>
-    <t>0.0010,0.9975,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.8242,0.0052,0.1637,0.0137</t>
-  </si>
-  <si>
-    <t>0.2022,0.0966,0.4324,0.3098</t>
-  </si>
-  <si>
-    <t>0.0003,0.0005,0.9992,0.0004</t>
-  </si>
-  <si>
-    <t>0.0591,0.0101,0.9443,0.0076</t>
-  </si>
-  <si>
-    <t>0.0134,0.0016,0.9819,0.0053</t>
-  </si>
-  <si>
-    <t>0.0242,0.0010,0.9658,0.0076</t>
-  </si>
-  <si>
-    <t>0.0055,0.0006,0.9856,0.0096</t>
-  </si>
-  <si>
-    <t>0.9114,0.1344,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.4951,0.6032,0.0136,0.0011</t>
-  </si>
-  <si>
-    <t>0.0018,0.0104,0.9890,0.0109</t>
-  </si>
-  <si>
-    <t>0.0026,0.9835,0.0577,0.0004</t>
-  </si>
-  <si>
-    <t>0.7955,0.0979,0.1075,0.0112</t>
-  </si>
-  <si>
-    <t>0.9757,0.0050,0.0112,0.0007</t>
-  </si>
-  <si>
-    <t>0.2087,0.7627,0.0268,0.0116</t>
-  </si>
-  <si>
-    <t>0.0176,0.9395,0.2215,0.0415</t>
-  </si>
-  <si>
-    <t>0.1186,0.4312,0.4355,0.0557</t>
-  </si>
-  <si>
-    <t>0.0131,0.0153,0.9859,0.0029</t>
-  </si>
-  <si>
-    <t>0.0363,0.0159,0.9573,0.0044</t>
-  </si>
-  <si>
-    <t>0.0092,0.0007,0.9920,0.0013</t>
-  </si>
-  <si>
-    <t>0.0025,0.1135,0.9758,0.0025</t>
-  </si>
-  <si>
-    <t>0.0002,0.9975,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.0049,0.0123,0.9886,0.0030</t>
-  </si>
-  <si>
-    <t>0.0120,0.6200,0.0063,0.9021</t>
-  </si>
-  <si>
-    <t>0.0004,0.9972,0.0004,0.0029</t>
-  </si>
-  <si>
-    <t>0.0015,0.9939,0.0136,0.0006</t>
-  </si>
-  <si>
-    <t>0.0013,0.9920,0.1278,0.0032</t>
-  </si>
-  <si>
-    <t>0.0056,0.0231,0.9693,0.0075</t>
-  </si>
-  <si>
-    <t>0.0059,0.0521,0.9870,0.0011</t>
-  </si>
-  <si>
-    <t>0.0986,0.0161,0.8983,0.0102</t>
-  </si>
-  <si>
-    <t>0.0143,0.0035,0.9702,0.0109</t>
-  </si>
-  <si>
-    <t>0.0515,0.0074,0.9661,0.0008</t>
-  </si>
-  <si>
-    <t>0.0127,0.0276,0.9686,0.0031</t>
-  </si>
-  <si>
-    <t>0.9852,0.0090,0.0047,0.0006</t>
-  </si>
-  <si>
-    <t>0.9880,0.0054,0.0035,0.0008</t>
-  </si>
-  <si>
-    <t>0.9838,0.0076,0.0027,0.0038</t>
-  </si>
-  <si>
-    <t>0.0023,0.0842,0.9891,0.0099</t>
-  </si>
-  <si>
-    <t>0.9884,0.0068,0.0028,0.0010</t>
-  </si>
-  <si>
-    <t>0.9964,0.0020,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9933,0.0026,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.0017,0.9453,0.9448,0.0009</t>
-  </si>
-  <si>
-    <t>0.0372,0.0280,0.9728,0.0014</t>
-  </si>
-  <si>
-    <t>0.0328,0.3052,0.8707,0.0138</t>
-  </si>
-  <si>
-    <t>0.0026,0.9201,0.8942,0.0015</t>
-  </si>
-  <si>
-    <t>0.0045,0.0340,0.9877,0.0045</t>
-  </si>
-  <si>
-    <t>0.0182,0.9749,0.0015,0.0010</t>
-  </si>
-  <si>
-    <t>0.0518,0.9670,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.8292,0.0131,0.2455,0.0048</t>
-  </si>
-  <si>
-    <t>0.7670,0.1549,0.1050,0.0255</t>
-  </si>
-  <si>
-    <t>0.0019,0.0051,0.9948,0.0017</t>
-  </si>
-  <si>
-    <t>0.0322,0.7888,0.6447,0.0108</t>
-  </si>
-  <si>
-    <t>0.0034,0.9404,0.8019,0.0013</t>
-  </si>
-  <si>
-    <t>0.0005,0.9961,0.0241,0.0002</t>
-  </si>
-  <si>
-    <t>0.0012,0.9796,0.5095,0.0021</t>
-  </si>
-  <si>
-    <t>0.0358,0.0007,0.0150,0.9659</t>
-  </si>
-  <si>
-    <t>0.0019,0.0010,0.0001,0.9988</t>
-  </si>
-  <si>
-    <t>0.0073,0.0007,0.0001,0.9971</t>
-  </si>
-  <si>
-    <t>0.0477,0.0018,0.0001,0.9820</t>
-  </si>
-  <si>
-    <t>0.0125,0.0006,0.0012,0.9933</t>
-  </si>
-  <si>
-    <t>0.0031,0.0043,0.0005,0.9970</t>
-  </si>
-  <si>
-    <t>0.0005,0.9755,0.9641,0.0003</t>
-  </si>
-  <si>
-    <t>0.0010,0.8973,0.9677,0.0005</t>
-  </si>
-  <si>
-    <t>0.0145,0.2408,0.7696,0.0101</t>
-  </si>
-  <si>
-    <t>0.0019,0.9593,0.8911,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.9842,0.9633,0.0001</t>
-  </si>
-  <si>
-    <t>0.0056,0.7279,0.9466,0.0047</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9927,0.0091,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9890,0.0120,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9958,0.0048,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9957,0.0022,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9988,0.0007,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9816,0.0283,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9906,0.0053,0.0022,0.0006</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0008,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9974,0.0019,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0081,0.0039,0.9870,0.0017</t>
-  </si>
-  <si>
-    <t>0.1905,0.1938,0.6837,0.0272</t>
-  </si>
-  <si>
-    <t>0.9235,0.0073,0.0740,0.0023</t>
-  </si>
-  <si>
-    <t>0.0945,0.0032,0.9165,0.0051</t>
-  </si>
-  <si>
-    <t>0.0015,0.9963,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.9983,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.0162,0.9742,0.0023,0.0043</t>
-  </si>
-  <si>
-    <t>0.0455,0.9458,0.0082,0.0026</t>
-  </si>
-  <si>
-    <t>0.0020,0.9954,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.0010,0.9969,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.7018,0.3405,0.0228,0.0021</t>
-  </si>
-  <si>
-    <t>0.5071,0.0437,0.5748,0.0316</t>
-  </si>
-  <si>
-    <t>0.1167,0.0035,0.9313,0.0020</t>
-  </si>
-  <si>
-    <t>0.5490,0.1703,0.3012,0.0257</t>
-  </si>
-  <si>
-    <t>0.5947,0.0125,0.5782,0.0039</t>
-  </si>
-  <si>
-    <t>0.0148,0.0862,0.0467,0.9523</t>
-  </si>
-  <si>
-    <t>0.0003,0.9985,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.0008,0.9960,0.0024,0.0012</t>
-  </si>
-  <si>
-    <t>0.0004,0.9962,0.0007,0.0090</t>
-  </si>
-  <si>
-    <t>0.0003,0.9822,0.9673,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.9951,0.0059,0.0004</t>
-  </si>
-  <si>
-    <t>0.9068,0.0869,0.0133,0.0005</t>
-  </si>
-  <si>
-    <t>0.8391,0.1591,0.0034,0.0068</t>
-  </si>
-  <si>
-    <t>0.9985,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9924,0.0029,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.9837,0.0055,0.0033,0.0028</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9947,0.0007,0.0002,0.0022</t>
-  </si>
-  <si>
-    <t>0.9932,0.0016,0.0010,0.0013</t>
-  </si>
-  <si>
-    <t>0.9833,0.0044,0.0069,0.0018</t>
-  </si>
-  <si>
-    <t>0.0027,0.7989,0.8823,0.0029</t>
-  </si>
-  <si>
-    <t>0.0095,0.4974,0.9291,0.0011</t>
-  </si>
-  <si>
-    <t>0.0290,0.2325,0.9254,0.0046</t>
-  </si>
-  <si>
-    <t>0.0112,0.1245,0.9680,0.0023</t>
-  </si>
-  <si>
-    <t>0.9965,0.0004,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.6611,0.0067,0.4794,0.0049</t>
-  </si>
-  <si>
-    <t>0.1611,0.0034,0.8557,0.0203</t>
-  </si>
-  <si>
-    <t>0.9472,0.0075,0.0362,0.0019</t>
-  </si>
-  <si>
-    <t>0.0570,0.0004,0.0002,0.9880</t>
-  </si>
-  <si>
-    <t>0.0002,0.0010,0.0001,0.9996</t>
-  </si>
-  <si>
-    <t>0.0027,0.0019,0.0003,0.9981</t>
-  </si>
-  <si>
-    <t>0.0576,0.0002,0.0001,0.9889</t>
-  </si>
-  <si>
-    <t>0.0010,0.9412,0.8326,0.0004</t>
-  </si>
-  <si>
-    <t>0.9947,0.0017,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.1774,0.8582,0.0024,0.0041</t>
-  </si>
-  <si>
-    <t>0.9777,0.0016,0.0033,0.0092</t>
-  </si>
-  <si>
-    <t>0.6202,0.4626,0.0154,0.0045</t>
-  </si>
-  <si>
-    <t>0.9731,0.0022,0.0029,0.0126</t>
-  </si>
-  <si>
-    <t>0.0955,0.0635,0.0077,0.8819</t>
-  </si>
-  <si>
-    <t>0.9935,0.0011,0.0008,0.0012</t>
-  </si>
-  <si>
-    <t>0.0104,0.0269,0.7927,0.4222</t>
-  </si>
-  <si>
-    <t>0.5305,0.0006,0.0015,0.7018</t>
-  </si>
-  <si>
-    <t>0.9036,0.0010,0.0008,0.1543</t>
-  </si>
-  <si>
-    <t>0.4999,0.4893,0.0161,0.0268</t>
-  </si>
-  <si>
-    <t>0.9875,0.0033,0.0025,0.0006</t>
-  </si>
-  <si>
-    <t>0.9837,0.0078,0.0031,0.0014</t>
-  </si>
-  <si>
-    <t>0.2740,0.6810,0.0840,0.0116</t>
-  </si>
-  <si>
-    <t>0.9369,0.0104,0.0716,0.0011</t>
-  </si>
-  <si>
-    <t>0.9644,0.0058,0.0203,0.0014</t>
-  </si>
-  <si>
-    <t>0.9976,0.0010,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9970,0.0017,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9932,0.0043,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9969,0.0007,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9937,0.0016,0.0007,0.0011</t>
-  </si>
-  <si>
-    <t>0.9902,0.0063,0.0012,0.0012</t>
-  </si>
-  <si>
-    <t>0.9972,0.0006,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9952,0.0005,0.0020,0.0004</t>
-  </si>
-  <si>
-    <t>0.4564,0.6000,0.0011,0.0037</t>
-  </si>
-  <si>
-    <t>0.6553,0.4367,0.0024,0.0027</t>
-  </si>
-  <si>
-    <t>0.8884,0.1135,0.0187,0.0020</t>
-  </si>
-  <si>
-    <t>0.5347,0.3698,0.3344,0.0364</t>
-  </si>
-  <si>
-    <t>0.9859,0.0183,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9822,0.0067,0.0053,0.0023</t>
-  </si>
-  <si>
-    <t>0.9939,0.0047,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9163,0.0730,0.0163,0.0080</t>
-  </si>
-  <si>
-    <t>0.0012,0.0163,0.9980,0.0006</t>
-  </si>
-  <si>
-    <t>0.9819,0.0042,0.0083,0.0005</t>
-  </si>
-  <si>
-    <t>0.0009,0.0020,0.9973,0.0009</t>
-  </si>
-  <si>
-    <t>0.0032,0.0102,0.9861,0.0056</t>
-  </si>
-  <si>
-    <t>0.0170,0.0022,0.9801,0.0056</t>
-  </si>
-  <si>
-    <t>0.0086,0.0162,0.9829,0.0009</t>
-  </si>
-  <si>
-    <t>0.0101,0.0029,0.9928,0.0003</t>
-  </si>
-  <si>
-    <t>0.0020,0.0018,0.9941,0.0036</t>
-  </si>
-  <si>
-    <t>0.0047,0.0077,0.9845,0.0058</t>
-  </si>
-  <si>
-    <t>0.2466,0.0773,0.7867,0.0044</t>
-  </si>
-  <si>
-    <t>0.1049,0.0020,0.9467,0.0019</t>
-  </si>
-  <si>
-    <t>0.1142,0.0648,0.8522,0.0232</t>
-  </si>
-  <si>
-    <t>0.3419,0.0480,0.7127,0.0017</t>
-  </si>
-  <si>
-    <t>0.3812,0.2659,0.4477,0.0213</t>
-  </si>
-  <si>
-    <t>0.3654,0.3863,0.2220,0.0244</t>
-  </si>
-  <si>
-    <t>0.8072,0.0366,0.1911,0.0166</t>
-  </si>
-  <si>
-    <t>0.0431,0.2555,0.7780,0.0260</t>
-  </si>
-  <si>
-    <t>0.4790,0.6502,0.0011,0.0013</t>
-  </si>
-  <si>
-    <t>0.1420,0.9254,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.7957,0.4209,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9818,0.0329,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.3914,0.6902,0.0011,0.0023</t>
-  </si>
-  <si>
-    <t>0.3733,0.5804,0.0413,0.0258</t>
-  </si>
-  <si>
-    <t>0.9853,0.0008,0.0081,0.0005</t>
-  </si>
-  <si>
-    <t>0.7832,0.0036,0.0662,0.0628</t>
-  </si>
-  <si>
-    <t>0.8564,0.0176,0.1145,0.0178</t>
-  </si>
-  <si>
-    <t>0.9340,0.0078,0.0378,0.0064</t>
-  </si>
-  <si>
-    <t>0.0020,0.0019,0.9820,0.0442</t>
-  </si>
-  <si>
-    <t>0.0075,0.0022,0.9884,0.0031</t>
-  </si>
-  <si>
-    <t>0.0084,0.0115,0.9862,0.0029</t>
-  </si>
-  <si>
-    <t>0.0640,0.0075,0.9099,0.0168</t>
-  </si>
-  <si>
-    <t>0.0266,0.1316,0.9151,0.0031</t>
-  </si>
-  <si>
-    <t>0.9919,0.0050,0.0002,0.0017</t>
-  </si>
-  <si>
-    <t>0.9974,0.0010,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9932,0.0049,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9883,0.0133,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9862,0.0102,0.0006,0.0015</t>
-  </si>
-  <si>
-    <t>0.9967,0.0013,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9966,0.0013,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9863,0.0064,0.0042,0.0022</t>
-  </si>
-  <si>
-    <t>0.0020,0.0175,0.9946,0.0013</t>
-  </si>
-  <si>
-    <t>0.0588,0.3737,0.7447,0.0390</t>
-  </si>
-  <si>
-    <t>0.6388,0.0029,0.2562,0.0306</t>
-  </si>
-  <si>
-    <t>0.0102,0.0001,0.9930,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.0612,0.9916,0.0066</t>
-  </si>
-  <si>
-    <t>0.3563,0.0422,0.5751,0.0006</t>
-  </si>
-  <si>
-    <t>0.0075,0.0085,0.9857,0.0033</t>
-  </si>
-  <si>
-    <t>0.0935,0.0059,0.9275,0.0029</t>
-  </si>
-  <si>
-    <t>0.0019,0.0020,0.9960,0.0006</t>
-  </si>
-  <si>
-    <t>0.0154,0.0290,0.9592,0.0109</t>
-  </si>
-  <si>
-    <t>0.0799,0.0081,0.9316,0.0037</t>
-  </si>
-  <si>
-    <t>0.9166,0.0013,0.0747,0.0050</t>
-  </si>
-  <si>
-    <t>0.9472,0.0009,0.0278,0.0053</t>
-  </si>
-  <si>
-    <t>0.8354,0.0009,0.2467,0.0028</t>
-  </si>
-  <si>
-    <t>0.9948,0.0042,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9978,0.0021,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9970,0.0011,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9954,0.0038,0.0003,0.0003</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.9669,0.0059,0.0010,0.0158</t>
+  </si>
+  <si>
+    <t>0.0238,0.0042,0.0025,0.9858</t>
+  </si>
+  <si>
+    <t>0.9493,0.0053,0.0011,0.0366</t>
+  </si>
+  <si>
+    <t>0.3932,0.0029,0.0005,0.7618</t>
+  </si>
+  <si>
+    <t>0.9987,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9969,0.0020,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0014,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9984,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9201,0.0033,0.1330,0.0008</t>
+  </si>
+  <si>
+    <t>0.0058,0.0106,0.9834,0.0102</t>
+  </si>
+  <si>
+    <t>0.1619,0.0144,0.8745,0.0005</t>
+  </si>
+  <si>
+    <t>0.0154,0.0162,0.9644,0.0087</t>
+  </si>
+  <si>
+    <t>0.9262,0.0032,0.0864,0.0019</t>
+  </si>
+  <si>
+    <t>0.0002,0.9987,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.9985,0.0045,0.0006</t>
+  </si>
+  <si>
+    <t>0.0050,0.9908,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.0034,0.9920,0.0040,0.0011</t>
+  </si>
+  <si>
+    <t>0.0015,0.9958,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.7392,0.0225,0.3208,0.0211</t>
+  </si>
+  <si>
+    <t>0.4301,0.0151,0.6301,0.0172</t>
+  </si>
+  <si>
+    <t>0.0022,0.0011,0.9963,0.0006</t>
+  </si>
+  <si>
+    <t>0.0823,0.0107,0.9116,0.0159</t>
+  </si>
+  <si>
+    <t>0.0044,0.0038,0.9936,0.0014</t>
+  </si>
+  <si>
+    <t>0.0041,0.0030,0.9847,0.0097</t>
+  </si>
+  <si>
+    <t>0.0124,0.0028,0.9748,0.0123</t>
+  </si>
+  <si>
+    <t>0.3153,0.7378,0.0026,0.0070</t>
+  </si>
+  <si>
+    <t>0.2988,0.7396,0.0177,0.0027</t>
+  </si>
+  <si>
+    <t>0.0040,0.0139,0.9836,0.0057</t>
+  </si>
+  <si>
+    <t>0.0051,0.9826,0.0168,0.0004</t>
+  </si>
+  <si>
+    <t>0.9155,0.0423,0.0132,0.0125</t>
+  </si>
+  <si>
+    <t>0.9684,0.0170,0.0107,0.0005</t>
+  </si>
+  <si>
+    <t>0.7395,0.2721,0.0232,0.0046</t>
+  </si>
+  <si>
+    <t>0.0147,0.9640,0.0587,0.0108</t>
+  </si>
+  <si>
+    <t>0.2337,0.1275,0.6118,0.0420</t>
+  </si>
+  <si>
+    <t>0.0274,0.0018,0.9671,0.0037</t>
+  </si>
+  <si>
+    <t>0.2448,0.0040,0.6580,0.0167</t>
+  </si>
+  <si>
+    <t>0.0979,0.0009,0.9160,0.0033</t>
+  </si>
+  <si>
+    <t>0.0078,0.0210,0.9830,0.0017</t>
+  </si>
+  <si>
+    <t>0.0024,0.9891,0.0051,0.0003</t>
+  </si>
+  <si>
+    <t>0.0083,0.0027,0.9815,0.0065</t>
+  </si>
+  <si>
+    <t>0.0080,0.4025,0.0043,0.9618</t>
+  </si>
+  <si>
+    <t>0.0030,0.9889,0.0012,0.0096</t>
+  </si>
+  <si>
+    <t>0.0006,0.9963,0.0458,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9985,0.0146,0.0013</t>
+  </si>
+  <si>
+    <t>0.0210,0.0359,0.9663,0.0040</t>
+  </si>
+  <si>
+    <t>0.0062,0.4201,0.9808,0.0030</t>
+  </si>
+  <si>
+    <t>0.0050,0.0026,0.9863,0.0065</t>
+  </si>
+  <si>
+    <t>0.0094,0.0025,0.9863,0.0024</t>
+  </si>
+  <si>
+    <t>0.0131,0.0531,0.9705,0.0017</t>
+  </si>
+  <si>
+    <t>0.0088,0.0142,0.9861,0.0018</t>
+  </si>
+  <si>
+    <t>0.9910,0.0073,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9878,0.0047,0.0046,0.0006</t>
+  </si>
+  <si>
+    <t>0.9932,0.0047,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.0024,0.0127,0.9903,0.0073</t>
+  </si>
+  <si>
+    <t>0.9941,0.0011,0.0032,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9892,0.0075,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.0029,0.9328,0.8766,0.0010</t>
+  </si>
+  <si>
+    <t>0.0095,0.0883,0.9734,0.0047</t>
+  </si>
+  <si>
+    <t>0.0167,0.0869,0.9580,0.0047</t>
+  </si>
+  <si>
+    <t>0.0005,0.9551,0.9709,0.0003</t>
+  </si>
+  <si>
+    <t>0.0052,0.0066,0.9825,0.0086</t>
+  </si>
+  <si>
+    <t>0.0212,0.9766,0.0026,0.0008</t>
+  </si>
+  <si>
+    <t>0.0135,0.9867,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.9188,0.0036,0.1999,0.0007</t>
+  </si>
+  <si>
+    <t>0.1462,0.8162,0.3552,0.0264</t>
+  </si>
+  <si>
+    <t>0.0058,0.0078,0.9922,0.0009</t>
+  </si>
+  <si>
+    <t>0.0074,0.9564,0.4460,0.0022</t>
+  </si>
+  <si>
+    <t>0.0081,0.8879,0.8477,0.0022</t>
+  </si>
+  <si>
+    <t>0.0033,0.9539,0.4447,0.0030</t>
+  </si>
+  <si>
+    <t>0.0030,0.9583,0.8194,0.0016</t>
+  </si>
+  <si>
+    <t>0.0123,0.0002,0.0028,0.9923</t>
+  </si>
+  <si>
+    <t>0.0019,0.0025,0.0001,0.9983</t>
+  </si>
+  <si>
+    <t>0.0056,0.0006,0.0001,0.9980</t>
+  </si>
+  <si>
+    <t>0.0447,0.0001,0.0000,0.9929</t>
+  </si>
+  <si>
+    <t>0.0042,0.0006,0.0008,0.9972</t>
+  </si>
+  <si>
+    <t>0.0033,0.0023,0.0003,0.9975</t>
+  </si>
+  <si>
+    <t>0.0021,0.9577,0.9119,0.0013</t>
+  </si>
+  <si>
+    <t>0.0008,0.9246,0.9756,0.0005</t>
+  </si>
+  <si>
+    <t>0.0012,0.9818,0.0726,0.0027</t>
+  </si>
+  <si>
+    <t>0.0011,0.9489,0.9740,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.9727,0.9760,0.0001</t>
+  </si>
+  <si>
+    <t>0.0133,0.7555,0.5865,0.0031</t>
+  </si>
+  <si>
+    <t>0.9975,0.0012,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9937,0.0094,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9928,0.0093,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9953,0.0022,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9952,0.0043,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9837,0.0194,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9764,0.0287,0.0024,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9975,0.0032,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0009,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0005,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.0748,0.0009,0.9556,0.0004</t>
+  </si>
+  <si>
+    <t>0.3828,0.0046,0.6100,0.0213</t>
+  </si>
+  <si>
+    <t>0.6894,0.0146,0.2250,0.0429</t>
+  </si>
+  <si>
+    <t>0.1360,0.0138,0.8863,0.0073</t>
+  </si>
+  <si>
+    <t>0.0009,0.9975,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.9971,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0084,0.9822,0.0026,0.0065</t>
+  </si>
+  <si>
+    <t>0.0064,0.9864,0.0037,0.0016</t>
+  </si>
+  <si>
+    <t>0.0037,0.9926,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.0004,0.9985,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.8822,0.1389,0.0137,0.0021</t>
+  </si>
+  <si>
+    <t>0.8875,0.0231,0.1066,0.0069</t>
+  </si>
+  <si>
+    <t>0.0219,0.0021,0.9814,0.0013</t>
+  </si>
+  <si>
+    <t>0.5776,0.0192,0.5232,0.0058</t>
+  </si>
+  <si>
+    <t>0.6714,0.0226,0.2380,0.0518</t>
+  </si>
+  <si>
+    <t>0.2786,0.2004,0.0579,0.6410</t>
+  </si>
+  <si>
+    <t>0.0002,0.9984,0.0042,0.0005</t>
+  </si>
+  <si>
+    <t>0.0013,0.9962,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.9947,0.0056,0.0259</t>
+  </si>
+  <si>
+    <t>0.0007,0.9613,0.9738,0.0003</t>
+  </si>
+  <si>
+    <t>0.0028,0.9939,0.0029,0.0003</t>
+  </si>
+  <si>
+    <t>0.9222,0.1134,0.0032,0.0010</t>
+  </si>
+  <si>
+    <t>0.8512,0.2003,0.0019,0.0016</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9956,0.0006,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9911,0.0017,0.0040,0.0010</t>
+  </si>
+  <si>
+    <t>0.9951,0.0006,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.9984,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9916,0.0023,0.0019,0.0011</t>
+  </si>
+  <si>
+    <t>0.9963,0.0005,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9863,0.0055,0.0035,0.0007</t>
+  </si>
+  <si>
+    <t>0.0023,0.8457,0.9359,0.0016</t>
+  </si>
+  <si>
+    <t>0.0044,0.3086,0.9466,0.0004</t>
+  </si>
+  <si>
+    <t>0.0210,0.0352,0.9767,0.0012</t>
+  </si>
+  <si>
+    <t>0.0487,0.0445,0.9493,0.0067</t>
+  </si>
+  <si>
+    <t>0.9904,0.0004,0.0027,0.0006</t>
+  </si>
+  <si>
+    <t>0.7735,0.0032,0.3153,0.0047</t>
+  </si>
+  <si>
+    <t>0.1321,0.0021,0.9183,0.0035</t>
+  </si>
+  <si>
+    <t>0.9671,0.0043,0.0216,0.0013</t>
+  </si>
+  <si>
+    <t>0.7491,0.0018,0.0002,0.4710</t>
+  </si>
+  <si>
+    <t>0.0004,0.0004,0.0001,0.9996</t>
+  </si>
+  <si>
+    <t>0.0025,0.0028,0.0003,0.9978</t>
+  </si>
+  <si>
+    <t>0.2259,0.0004,0.0001,0.9389</t>
+  </si>
+  <si>
+    <t>0.0032,0.8710,0.5900,0.0014</t>
+  </si>
+  <si>
+    <t>0.9944,0.0008,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.0039,0.9893,0.0012,0.0055</t>
+  </si>
+  <si>
+    <t>0.9768,0.0077,0.0041,0.0053</t>
+  </si>
+  <si>
+    <t>0.0101,0.9831,0.0012,0.0011</t>
+  </si>
+  <si>
+    <t>0.9966,0.0005,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.0748,0.0160,0.0097,0.9516</t>
+  </si>
+  <si>
+    <t>0.9940,0.0007,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.0447,0.0036,0.7096,0.3176</t>
+  </si>
+  <si>
+    <t>0.4930,0.0010,0.0036,0.5908</t>
+  </si>
+  <si>
+    <t>0.9681,0.0015,0.0007,0.0240</t>
+  </si>
+  <si>
+    <t>0.6579,0.1931,0.1692,0.0066</t>
+  </si>
+  <si>
+    <t>0.9943,0.0010,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9546,0.0247,0.0125,0.0049</t>
+  </si>
+  <si>
+    <t>0.2984,0.5751,0.0844,0.0041</t>
+  </si>
+  <si>
+    <t>0.8489,0.0223,0.1758,0.0017</t>
+  </si>
+  <si>
+    <t>0.9743,0.0179,0.0051,0.0009</t>
   </si>
   <si>
     <t>0.9988,0.0003,0.0000,0.0003</t>
   </si>
   <si>
-    <t>0.9957,0.0026,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0015,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9959,0.0023,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.0099,0.0233,0.9657,0.0062</t>
-  </si>
-  <si>
-    <t>0.0112,0.0081,0.9878,0.0009</t>
-  </si>
-  <si>
-    <t>0.0175,0.0180,0.9576,0.0032</t>
-  </si>
-  <si>
-    <t>0.0810,0.0130,0.9026,0.0089</t>
-  </si>
-  <si>
-    <t>0.0177,0.0012,0.9897,0.0004</t>
-  </si>
-  <si>
-    <t>0.0091,0.0039,0.9721,0.0397</t>
-  </si>
-  <si>
-    <t>0.0667,0.0038,0.9115,0.0260</t>
-  </si>
-  <si>
-    <t>0.0271,0.0041,0.8808,0.0441</t>
-  </si>
-  <si>
-    <t>0.6692,0.0017,0.0068,0.3589</t>
-  </si>
-  <si>
-    <t>0.0218,0.0090,0.0025,0.9864</t>
-  </si>
-  <si>
-    <t>0.0703,0.0004,0.0008,0.9772</t>
-  </si>
-  <si>
-    <t>0.0042,0.0001,0.0001,0.9989</t>
-  </si>
-  <si>
-    <t>0.0033,0.0005,0.0004,0.9980</t>
-  </si>
-  <si>
-    <t>0.6527,0.0186,0.0041,0.3746</t>
+    <t>0.9983,0.0003,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9963,0.0011,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9943,0.0002,0.0002,0.0037</t>
+  </si>
+  <si>
+    <t>0.9932,0.0015,0.0006,0.0017</t>
+  </si>
+  <si>
+    <t>0.9937,0.0033,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9944,0.0006,0.0003,0.0027</t>
+  </si>
+  <si>
+    <t>0.9947,0.0007,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.7619,0.2456,0.0036,0.0069</t>
+  </si>
+  <si>
+    <t>0.2919,0.7566,0.0047,0.0055</t>
+  </si>
+  <si>
+    <t>0.3573,0.7382,0.0034,0.0006</t>
+  </si>
+  <si>
+    <t>0.7189,0.2394,0.1407,0.0089</t>
+  </si>
+  <si>
+    <t>0.9944,0.0039,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9907,0.0011,0.0043,0.0005</t>
+  </si>
+  <si>
+    <t>0.9926,0.0034,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.9874,0.0073,0.0019,0.0009</t>
+  </si>
+  <si>
+    <t>0.0050,0.0318,0.9926,0.0026</t>
+  </si>
+  <si>
+    <t>0.9759,0.0157,0.0062,0.0014</t>
+  </si>
+  <si>
+    <t>0.0060,0.0009,0.9962,0.0001</t>
+  </si>
+  <si>
+    <t>0.0029,0.0300,0.9917,0.0037</t>
+  </si>
+  <si>
+    <t>0.0070,0.0026,0.9844,0.0109</t>
+  </si>
+  <si>
+    <t>0.0287,0.3922,0.7978,0.0024</t>
+  </si>
+  <si>
+    <t>0.0028,0.0027,0.9956,0.0005</t>
+  </si>
+  <si>
+    <t>0.0018,0.0001,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.0132,0.9904,0.0052</t>
+  </si>
+  <si>
+    <t>0.0613,0.0082,0.9056,0.0367</t>
+  </si>
+  <si>
+    <t>0.2760,0.0076,0.8374,0.0013</t>
+  </si>
+  <si>
+    <t>0.0867,0.1406,0.8589,0.0069</t>
+  </si>
+  <si>
+    <t>0.1088,0.1625,0.8248,0.0053</t>
+  </si>
+  <si>
+    <t>0.1397,0.1073,0.8233,0.0124</t>
+  </si>
+  <si>
+    <t>0.3244,0.0312,0.7301,0.0058</t>
+  </si>
+  <si>
+    <t>0.3966,0.1329,0.5657,0.0362</t>
+  </si>
+  <si>
+    <t>0.1943,0.1322,0.6586,0.0541</t>
+  </si>
+  <si>
+    <t>0.6691,0.5469,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.2229,0.8686,0.0019,0.0008</t>
+  </si>
+  <si>
+    <t>0.8384,0.2311,0.0017,0.0020</t>
+  </si>
+  <si>
+    <t>0.9804,0.0205,0.0014,0.0011</t>
+  </si>
+  <si>
+    <t>0.6476,0.5229,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.3125,0.7305,0.0177,0.0038</t>
+  </si>
+  <si>
+    <t>0.9961,0.0001,0.0027,0.0000</t>
+  </si>
+  <si>
+    <t>0.8497,0.0280,0.1018,0.0148</t>
+  </si>
+  <si>
+    <t>0.9534,0.0061,0.0455,0.0008</t>
+  </si>
+  <si>
+    <t>0.9660,0.0060,0.0068,0.0060</t>
+  </si>
+  <si>
+    <t>0.0068,0.0041,0.9772,0.0146</t>
+  </si>
+  <si>
+    <t>0.0100,0.0187,0.9789,0.0039</t>
+  </si>
+  <si>
+    <t>0.0195,0.0065,0.9764,0.0021</t>
+  </si>
+  <si>
+    <t>0.0624,0.0022,0.9463,0.0031</t>
+  </si>
+  <si>
+    <t>0.0221,0.5471,0.7438,0.0042</t>
+  </si>
+  <si>
+    <t>0.9959,0.0015,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9974,0.0005,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9948,0.0041,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9935,0.0053,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9825,0.0134,0.0010,0.0024</t>
+  </si>
+  <si>
+    <t>0.9973,0.0009,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9916,0.0049,0.0010,0.0012</t>
+  </si>
+  <si>
+    <t>0.9977,0.0003,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.0085,0.1982,0.9773,0.0053</t>
+  </si>
+  <si>
+    <t>0.0966,0.0706,0.9061,0.0040</t>
+  </si>
+  <si>
+    <t>0.9646,0.0029,0.0197,0.0027</t>
+  </si>
+  <si>
+    <t>0.0162,0.0009,0.9880,0.0005</t>
+  </si>
+  <si>
+    <t>0.0006,0.0084,0.9947,0.0033</t>
+  </si>
+  <si>
+    <t>0.0246,0.0830,0.9345,0.0046</t>
+  </si>
+  <si>
+    <t>0.0018,0.0063,0.9934,0.0037</t>
+  </si>
+  <si>
+    <t>0.0111,0.0151,0.9493,0.0241</t>
+  </si>
+  <si>
+    <t>0.0007,0.0034,0.9973,0.0007</t>
+  </si>
+  <si>
+    <t>0.0216,0.0220,0.9375,0.0294</t>
+  </si>
+  <si>
+    <t>0.1029,0.0812,0.8465,0.0093</t>
+  </si>
+  <si>
+    <t>0.6055,0.0008,0.3482,0.0102</t>
+  </si>
+  <si>
+    <t>0.8272,0.0017,0.2214,0.0035</t>
+  </si>
+  <si>
+    <t>0.9234,0.0053,0.0571,0.0046</t>
+  </si>
+  <si>
+    <t>0.9896,0.0120,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9886,0.0178,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9948,0.0055,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9926,0.0038,0.0031,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0008,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9959,0.0050,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0024,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0016,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0381,0.0573,0.9126,0.0042</t>
+  </si>
+  <si>
+    <t>0.0313,0.0319,0.9628,0.0043</t>
+  </si>
+  <si>
+    <t>0.0211,0.0116,0.9570,0.0100</t>
+  </si>
+  <si>
+    <t>0.0350,0.0303,0.9482,0.0028</t>
+  </si>
+  <si>
+    <t>0.0144,0.0084,0.9744,0.0021</t>
+  </si>
+  <si>
+    <t>0.0286,0.0048,0.9640,0.0131</t>
+  </si>
+  <si>
+    <t>0.0443,0.0129,0.9395,0.0172</t>
+  </si>
+  <si>
+    <t>0.0298,0.0057,0.9284,0.0218</t>
+  </si>
+  <si>
+    <t>0.6631,0.0024,0.0154,0.3023</t>
+  </si>
+  <si>
+    <t>0.5793,0.0026,0.0006,0.6388</t>
+  </si>
+  <si>
+    <t>0.0993,0.0008,0.0016,0.9582</t>
+  </si>
+  <si>
+    <t>0.0041,0.0001,0.0002,0.9984</t>
+  </si>
+  <si>
+    <t>0.0047,0.0001,0.0004,0.9977</t>
+  </si>
+  <si>
+    <t>0.5225,0.0371,0.0060,0.4041</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2273,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2385,7 @@
         <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2928,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2956,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3141,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3547,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3558,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>272</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3855,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3950,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4093,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4135,7 @@
         <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4205,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4356,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4384,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4625,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4639,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4678,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4695,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4706,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4762,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4779,7 @@
         <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4821,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4902,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5045,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5462,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
